--- a/dev/molgenis/D5.3 - EUCAIM - Molgenis metadata model - september 2026.xlsx
+++ b/dev/molgenis/D5.3 - EUCAIM - Molgenis metadata model - september 2026.xlsx
@@ -1201,14 +1201,6 @@
       <c r="G24" t="b">
         <v>1</v>
       </c>
-      <c r="O24" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>String([…name].sort().join('\0').split('').reduce((h, c) =&gt; Math.imul(h, 33) ^ c.charCodeAt(0), 5381) &gt;&gt;&gt; 0)</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4145,14 +4137,6 @@
       <c r="G109" t="b">
         <v>1</v>
       </c>
-      <c r="O109" t="b">
-        <v>0</v>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>fn.replaceAll(' ', '').toLowerCase()</t>
-        </is>
-      </c>
       <c r="Q109" s="4" t="n"/>
     </row>
     <row r="110">
@@ -5550,14 +5534,7 @@
       <c r="G153" t="b">
         <v>1</v>
       </c>
-      <c r="O153" t="b">
-        <v>0</v>
-      </c>
-      <c r="P153" s="15" t="inlineStr">
-        <is>
-          <t>String([...label].sort().join('\0').split('').reduce((h, c) =&gt; Math.imul(h, 33) ^ c.charCodeAt(0), 5381) &gt;&gt;&gt; 0)</t>
-        </is>
-      </c>
+      <c r="P153" s="15" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5611,14 +5588,7 @@
       <c r="G155" t="b">
         <v>1</v>
       </c>
-      <c r="O155" t="b">
-        <v>0</v>
-      </c>
-      <c r="P155" s="15" t="inlineStr">
-        <is>
-          <t>String([...description].sort().join('\0').split('').reduce((h, c) =&gt; Math.imul(h, 33) ^ c.charCodeAt(0), 5381) &gt;&gt;&gt; 0)</t>
-        </is>
-      </c>
+      <c r="P155" s="15" t="n"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
